--- a/main/ig/StructureDefinition-ror-measurereport.xlsx
+++ b/main/ig/StructureDefinition-ror-measurereport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T15:54:27+00:00</t>
+    <t>2026-01-30T10:12:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-measurereport.xlsx
+++ b/main/ig/StructureDefinition-ror-measurereport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:12:59+00:00</t>
+    <t>2026-03-09T13:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-measurereport.xlsx
+++ b/main/ig/StructureDefinition-ror-measurereport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T13:22:43+00:00</t>
+    <t>2026-03-17T11:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-measurereport.xlsx
+++ b/main/ig/StructureDefinition-ror-measurereport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T11:12:47+00:00</t>
+    <t>2026-03-23T15:20:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-measurereport.xlsx
+++ b/main/ig/StructureDefinition-ror-measurereport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T15:20:38+00:00</t>
+    <t>2026-03-24T09:51:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-measurereport.xlsx
+++ b/main/ig/StructureDefinition-ror-measurereport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-1</t>
+    <t>0.7.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T09:51:35+00:00</t>
+    <t>2026-03-24T10:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-measurereport.xlsx
+++ b/main/ig/StructureDefinition-ror-measurereport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:33:49+00:00</t>
+    <t>2026-04-29T13:16:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-measurereport.xlsx
+++ b/main/ig/StructureDefinition-ror-measurereport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T13:16:27+00:00</t>
+    <t>2026-04-29T15:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-measurereport.xlsx
+++ b/main/ig/StructureDefinition-ror-measurereport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:13+00:00</t>
+    <t>2026-04-29T15:21:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-measurereport.xlsx
+++ b/main/ig/StructureDefinition-ror-measurereport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:33+00:00</t>
+    <t>2026-07-23T07:54:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -362,7 +362,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -547,7 +547,7 @@
     <t>MeasureReport.measure</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(Measure)
+    <t xml:space="preserve">canonical(Measure|4.0.1)
 </t>
   </si>
   <si>
@@ -770,7 +770,7 @@
     <t>The type of population (e.g. initial, numerator, denominator, etc.).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/measure-population</t>
+    <t>http://hl7.org/fhir/ValueSet/measure-population|4.0.1</t>
   </si>
   <si>
     <t>MeasureReport.group.population.count</t>
@@ -792,7 +792,7 @@
     <t>MeasureReport.group.population.subjectResults</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(List)
+    <t xml:space="preserve">Reference(List|4.0.1)
 </t>
   </si>
   <si>
@@ -960,7 +960,7 @@
     <t>MeasureReport.evaluatedResource</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1285,17 +1285,17 @@
   <dimension ref="A1:AL57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="65.3359375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="65.3359375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="56.015625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="56.015625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="248.734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1304,24 +1304,24 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="139.44140625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.8515625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="61.453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="119.546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.171875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="52.68359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="143.74609375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="123.23828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2410,7 +2410,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -2520,7 +2520,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>153</v>
       </c>
@@ -2628,7 +2628,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>161</v>
       </c>
@@ -2736,7 +2736,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>169</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>183</v>
       </c>
@@ -3166,7 +3166,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>193</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>225</v>
       </c>
@@ -4674,7 +4674,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>250</v>
       </c>
@@ -7476,12 +7476,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AL57">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/main/ig/StructureDefinition-ror-measurereport.xlsx
+++ b/main/ig/StructureDefinition-ror-measurereport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T07:54:45+00:00</t>
+    <t>2026-07-23T08:00:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-measurereport.xlsx
+++ b/main/ig/StructureDefinition-ror-measurereport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:00:07+00:00</t>
+    <t>2026-07-23T08:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
